--- a/Deterministic/Model Files/Segment Test/data/producer_ratios.xlsx
+++ b/Deterministic/Model Files/Segment Test/data/producer_ratios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Model Files/L-Shaped/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uark-my.sharepoint.com/personal/uhorchak_uark_edu/Documents/Desktop/Vaccine_Tender/Deterministic/Model Files/Segment Test/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{243B714B-BD6B-4548-BBF5-8AECB1072816}"/>
+  <xr:revisionPtr revIDLastSave="297" documentId="8_{CA986233-5C84-4EAA-B96B-661799E682FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACC5AE92-5C5C-4775-A0B1-BB69B2D63908}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{CCA420AF-4493-4C79-A19E-AC0C61F28524}"/>
   </bookViews>
   <sheets>
     <sheet name="starting_cap" sheetId="1" r:id="rId1"/>
@@ -692,10 +692,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1168,8 +1164,8 @@
   <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
@@ -1728,4 +1724,10 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{79c742c4-e61c-4fa5-be89-a3cb566a80d1}" enabled="0" method="" siteId="{79c742c4-e61c-4fa5-be89-a3cb566a80d1}" removed="1"/>
+</clbl:labelList>
 </file>